--- a/planilhas_competidores/Lorenzo_previsoes.xlsx
+++ b/planilhas_competidores/Lorenzo_previsoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479BCCBB-02A7-4F37-9E9E-F3D4019DD04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2B5300-64E4-4E97-A268-91479F86D71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1916,7 +1916,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>84</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>90</v>
       </c>
@@ -1961,8 +1961,14 @@
       <c r="G50" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <v>3</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -1985,7 +1991,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>90</v>
       </c>
@@ -2008,7 +2014,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>90</v>
       </c>
@@ -2031,7 +2037,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>90</v>
       </c>
@@ -2054,7 +2060,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -2077,7 +2083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -2100,7 +2106,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -2123,7 +2129,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>98</v>
       </c>
@@ -2146,7 +2152,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -2169,7 +2175,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>98</v>
       </c>
@@ -2192,7 +2198,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>98</v>
       </c>
@@ -2215,7 +2221,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>105</v>
       </c>
@@ -2238,7 +2244,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -2261,7 +2267,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>105</v>
       </c>

--- a/planilhas_competidores/Lorenzo_previsoes.xlsx
+++ b/planilhas_competidores/Lorenzo_previsoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2B5300-64E4-4E97-A268-91479F86D71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78197305-33B1-41BF-BA72-E574A6B3CE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -819,6 +819,12 @@
       <c r="G4" t="s">
         <v>21</v>
       </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -842,6 +848,12 @@
       <c r="G5" t="s">
         <v>18</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -969,6 +981,12 @@
       <c r="G10" t="s">
         <v>34</v>
       </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -992,6 +1010,12 @@
       <c r="G11" t="s">
         <v>36</v>
       </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1119,6 +1143,12 @@
       <c r="G16" t="s">
         <v>44</v>
       </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1142,6 +1172,12 @@
       <c r="G17" t="s">
         <v>46</v>
       </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -1269,6 +1305,12 @@
       <c r="G22" t="s">
         <v>37</v>
       </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1292,6 +1334,12 @@
       <c r="G23" t="s">
         <v>56</v>
       </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -1569,6 +1617,12 @@
       <c r="G34" t="s">
         <v>62</v>
       </c>
+      <c r="H34">
+        <v>4</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -1990,6 +2044,12 @@
       <c r="G51" t="s">
         <v>44</v>
       </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>3</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -2105,6 +2165,12 @@
       <c r="G56" t="s">
         <v>68</v>
       </c>
+      <c r="H56">
+        <v>4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -2128,6 +2194,12 @@
       <c r="G57" t="s">
         <v>33</v>
       </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>3</v>
+      </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -2243,6 +2315,12 @@
       <c r="G62" t="s">
         <v>62</v>
       </c>
+      <c r="H62">
+        <v>4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -2266,6 +2344,12 @@
       <c r="G63" t="s">
         <v>14</v>
       </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>3</v>
+      </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -2290,7 +2374,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>105</v>
       </c>
@@ -2313,7 +2397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>105</v>
       </c>
@@ -2336,7 +2420,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>105</v>
       </c>
@@ -2359,7 +2443,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>111</v>
       </c>
@@ -2381,8 +2465,14 @@
       <c r="G68" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>111</v>
       </c>
@@ -2404,8 +2494,14 @@
       <c r="G69" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69">
+        <v>3</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>111</v>
       </c>
@@ -2428,7 +2524,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>111</v>
       </c>
@@ -2451,7 +2547,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>111</v>
       </c>
@@ -2474,7 +2570,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>111</v>
       </c>

--- a/planilhas_competidores/Lorenzo_previsoes.xlsx
+++ b/planilhas_competidores/Lorenzo_previsoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78197305-33B1-41BF-BA72-E574A6B3CE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD003DB6-D9B4-42DD-8097-2043FE4ACF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1467,6 +1467,12 @@
       <c r="G28" t="s">
         <v>29</v>
       </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1490,6 +1496,12 @@
       <c r="G29" t="s">
         <v>68</v>
       </c>
+      <c r="H29">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -1646,6 +1658,12 @@
       <c r="G35" t="s">
         <v>24</v>
       </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -1773,6 +1791,12 @@
       <c r="G40" t="s">
         <v>34</v>
       </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -1796,6 +1820,12 @@
       <c r="G41" t="s">
         <v>36</v>
       </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -1923,6 +1953,12 @@
       <c r="G46" t="s">
         <v>21</v>
       </c>
+      <c r="H46">
+        <v>4</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -1945,6 +1981,12 @@
       </c>
       <c r="G47" t="s">
         <v>47</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">

--- a/planilhas_competidores/Lorenzo_previsoes.xlsx
+++ b/planilhas_competidores/Lorenzo_previsoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD003DB6-D9B4-42DD-8097-2043FE4ACF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0794E322-75E7-4E43-8A7F-D62F17527C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10035" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2115,6 +2115,12 @@
       <c r="G52" t="s">
         <v>46</v>
       </c>
+      <c r="H52">
+        <v>7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2138,6 +2144,12 @@
       <c r="G53" t="s">
         <v>41</v>
       </c>
+      <c r="H53">
+        <v>4</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -2265,6 +2277,12 @@
       <c r="G58" t="s">
         <v>72</v>
       </c>
+      <c r="H58">
+        <v>4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -2287,6 +2305,12 @@
       </c>
       <c r="G59" t="s">
         <v>56</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">

--- a/planilhas_competidores/Lorenzo_previsoes.xlsx
+++ b/planilhas_competidores/Lorenzo_previsoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0794E322-75E7-4E43-8A7F-D62F17527C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C0666C-AFFA-4468-AAD2-14095910BE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10035" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2439,6 +2439,12 @@
       <c r="G64" t="s">
         <v>62</v>
       </c>
+      <c r="H64">
+        <v>4</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
@@ -2462,6 +2468,12 @@
       <c r="G65" t="s">
         <v>18</v>
       </c>
+      <c r="H65">
+        <v>5</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
@@ -2589,6 +2601,12 @@
       <c r="G70" t="s">
         <v>44</v>
       </c>
+      <c r="H70">
+        <v>6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -2611,6 +2629,12 @@
       </c>
       <c r="G71" t="s">
         <v>29</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
